--- a/artfynd/A 52540-2025 artfynd.xlsx
+++ b/artfynd/A 52540-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769165</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129769597</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52540-2025 artfynd.xlsx
+++ b/artfynd/A 52540-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769165</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129769597</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52540-2025 artfynd.xlsx
+++ b/artfynd/A 52540-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769165</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129769597</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52540-2025 artfynd.xlsx
+++ b/artfynd/A 52540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129769165</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129769597</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,6 +918,251 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129769648</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>512444</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6295005</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129769899</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512418</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6294986</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>

--- a/artfynd/A 52540-2025 artfynd.xlsx
+++ b/artfynd/A 52540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769597</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769648</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,8 +1187,19 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769899</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>